--- a/naver-place-crawler/results_derma/군위군_피부과.xlsx
+++ b/naver-place-crawler/results_derma/군위군_피부과.xlsx
@@ -564,25 +564,25 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>제이엘의원</t>
+          <t>아미엘피부과</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1405-7710</t>
+          <t>054-475-7582</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경상북도 구미시 산동읍 신당1로4길 20 탑클래스빌딩 4층</t>
+          <t>경상북도 구미시 옥계북로 40</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>http://www.jlskin.co.kr/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -592,7 +592,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -608,7 +608,7 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -617,13 +617,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>385</v>
+        <v>18</v>
       </c>
       <c r="Q2" t="n">
-        <v>9</v>
+        <v>382</v>
       </c>
       <c r="R2" t="n">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -632,17 +632,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>37996584</t>
+          <t>32658915</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37996584</t>
+          <t>https://m.place.naver.com/place/32658915</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -654,12 +654,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>이지함의원</t>
+          <t>제이케이아름다운의원</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>heon6868@naver.com</t>
+          <t>hermesjk1@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -667,12 +667,12 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경상북도 구미시 옥계북로 36 202호 이지함의원</t>
+          <t>경상북도 구미시 인동가산로 31 쌍둥이빌딩 5층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/heon6868</t>
+          <t>https://blog.naver.com/hermesjk1</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -707,13 +707,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>47</v>
+        <v>186</v>
       </c>
       <c r="Q3" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>60</v>
+        <v>188</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -722,17 +722,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>35623875</t>
+          <t>12913832</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35623875</t>
+          <t>https://m.place.naver.com/place/12913832</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -744,43 +744,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>타토아의원 구미</t>
+          <t>제이엘의원</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>doctor_oh89@naver.com</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>tatoamygumi@gmail.com</t>
-        </is>
-      </c>
+          <t>nose10542@naver.com</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1347-9396</t>
+          <t>0507-1405-7710</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경상북도 구미시 산동읍 신당1로3길 17-6 3층</t>
+          <t>경상북도 구미시 산동읍 신당1로4길 20 탑클래스빌딩 4층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://tatoagm.co.kr</t>
+          <t>http://www.jlskin.co.kr/</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -805,13 +801,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>726</v>
+        <v>385</v>
       </c>
       <c r="Q4" t="n">
-        <v>63</v>
+        <v>9</v>
       </c>
       <c r="R4" t="n">
-        <v>789</v>
+        <v>394</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -820,17 +816,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2069909268</t>
+          <t>37996584</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2069909268</t>
+          <t>https://m.place.naver.com/place/37996584</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -842,29 +838,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>프렌즈의원</t>
+          <t>리움피부과의원</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>kidswell13@naver.com</t>
+          <t>riumskin01@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>054-474-7980</t>
+          <t>054-476-1010</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경상북도 구미시 인동가산로 5 천복빌딩 7층</t>
+          <t>경상북도 구미시 산호대로29길 20-7 태양주빌딩 2층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>http://www.friendscl.com/</t>
+          <t>http://www.riumskin.com</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -879,7 +875,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -895,17 +891,17 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>209</v>
+        <v>701</v>
       </c>
       <c r="Q5" t="n">
-        <v>814</v>
+        <v>638</v>
       </c>
       <c r="R5" t="n">
-        <v>1023</v>
+        <v>1339</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -914,17 +910,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>21230228</t>
+          <t>1767419444</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/21230228</t>
+          <t>https://m.place.naver.com/place/1767419444</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -993,13 +989,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1639</v>
+        <v>1657</v>
       </c>
       <c r="Q6" t="n">
         <v>53</v>
       </c>
       <c r="R6" t="n">
-        <v>1692</v>
+        <v>1710</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1018,7 +1014,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1030,44 +1026,40 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>미즈의원</t>
+          <t>이지함의원</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>october2nd_@naver.com</t>
+          <t>heon6868@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>054-458-7582</t>
-        </is>
-      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경상북도 구미시 산호대로29길 20-12 4층</t>
+          <t>경상북도 구미시 옥계북로 36 202호 이지함의원</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>http://mizskin.net/</t>
+          <t>https://blog.naver.com/heon6868</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1078,7 +1070,7 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1087,13 +1079,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>375</v>
+        <v>47</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="R7" t="n">
-        <v>375</v>
+        <v>60</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1102,17 +1094,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>36476632</t>
+          <t>35623875</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36476632</t>
+          <t>https://m.place.naver.com/place/35623875</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1124,26 +1116,34 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>에스의원</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
+          <t>프렌즈의원</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>kidswell13@naver.com</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>054-474-7980</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경상북도 구미시 인동36길 6</t>
+          <t>경상북도 구미시 인동가산로 5 천복빌딩 7층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.friendscl.com/</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1164,7 +1164,7 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1173,13 +1173,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>135</v>
+        <v>209</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>820</v>
       </c>
       <c r="R8" t="n">
-        <v>136</v>
+        <v>1029</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1188,17 +1188,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>13293913</t>
+          <t>21230228</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13293913</t>
+          <t>https://m.place.naver.com/place/21230228</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1210,25 +1210,25 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>제이케이아름다운의원</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>hermesjk1@naver.com</t>
-        </is>
-      </c>
+          <t>인동씨엔케이의원</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>054-471-0772</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경상북도 구미시 인동가산로 31 쌍둥이빌딩 5층</t>
+          <t>경상북도 구미시 인동가산로 23 3층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/hermesjk1</t>
+          <t>http://uroderm.net</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1263,13 +1263,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>186</v>
+        <v>259</v>
       </c>
       <c r="Q9" t="n">
-        <v>2</v>
+        <v>63</v>
       </c>
       <c r="R9" t="n">
-        <v>188</v>
+        <v>322</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1278,17 +1278,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>12913832</t>
+          <t>1060896022</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/12913832</t>
+          <t>https://m.place.naver.com/place/1060896022</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1300,29 +1300,33 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>리움피부과의원</t>
+          <t>타토아의원 구미</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>riumskin01@naver.com</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>doctor_oh89@naver.com</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>tatoamygumi@gmail.com</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>054-476-1010</t>
+          <t>0507-1347-9396</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경상북도 구미시 산호대로29길 20-7 태양주빌딩 2층</t>
+          <t>경상북도 구미시 산동읍 신당1로3길 17-6 3층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>http://www.riumskin.com</t>
+          <t>https://tatoagm.co.kr</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1337,7 +1341,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1353,17 +1357,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>699</v>
+        <v>808</v>
       </c>
       <c r="Q10" t="n">
-        <v>635</v>
+        <v>63</v>
       </c>
       <c r="R10" t="n">
-        <v>1334</v>
+        <v>871</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1372,17 +1376,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1767419444</t>
+          <t>2069909268</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1767419444</t>
+          <t>https://m.place.naver.com/place/2069909268</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1394,34 +1398,34 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>아미엘피부과</t>
+          <t>미즈의원</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>eazyzoo@naver.com</t>
+          <t>october2nd_@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>054-475-7582</t>
+          <t>054-458-7582</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경상북도 구미시 옥계북로 40</t>
+          <t>경상북도 구미시 산호대로29길 20-12 4층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://mizskin.net/</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1442,7 +1446,7 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1451,13 +1455,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>18</v>
+        <v>376</v>
       </c>
       <c r="Q11" t="n">
-        <v>382</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>400</v>
+        <v>376</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1466,17 +1470,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>32658915</t>
+          <t>36476632</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32658915</t>
+          <t>https://m.place.naver.com/place/36476632</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1488,25 +1492,25 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>인동씨엔케이의원</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr"/>
+          <t>에스의원</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>cosmedi1@naver.com</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>054-471-0772</t>
-        </is>
-      </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>경상북도 구미시 인동가산로 23 3층</t>
+          <t>경상북도 구미시 인동36길 6</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>http://uroderm.net</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1516,12 +1520,12 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1541,13 +1545,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>259</v>
+        <v>135</v>
       </c>
       <c r="Q12" t="n">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>315</v>
+        <v>136</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1556,17 +1560,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1060896022</t>
+          <t>13293913</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1060896022</t>
+          <t>https://m.place.naver.com/place/13293913</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1638,10 +1642,10 @@
         <v>553</v>
       </c>
       <c r="Q13" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="R13" t="n">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1660,7 +1664,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1672,29 +1676,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>아미엘연합의원</t>
+          <t>오앤정연합의원</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>whitekmg1@naver.com</t>
+          <t>ilove_hp@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>054-475-7582</t>
+          <t>054-464-7575</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>경상북도 구미시 옥계북로 40</t>
+          <t>경상북도 구미시 인동36길 15 2층3층</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>http://www.amiel.co.kr/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1704,12 +1708,12 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1720,7 +1724,7 @@
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1729,13 +1733,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>528</v>
+        <v>336</v>
       </c>
       <c r="Q14" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="R14" t="n">
-        <v>539</v>
+        <v>340</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1744,17 +1748,17 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>20713357</t>
+          <t>1505760191</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20713357</t>
+          <t>https://m.place.naver.com/place/1505760191</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1766,39 +1770,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>서울아산속내과의원</t>
+          <t>365늘속편한내과의원</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>seoulasansok7582@naver.com</t>
+          <t>wgsok@naver.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>054-476-7575</t>
+          <t>054-974-7070</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>경상북도 구미시 인동36길 6 2층 201호</t>
+          <t>경상북도 칠곡군 왜관읍 중앙로 232 3층</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>http://www.seoulasansok.com</t>
+          <t>http://www.365neulsok.co.kr/</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1814,7 +1818,7 @@
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1823,13 +1827,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>98</v>
+        <v>340</v>
       </c>
       <c r="Q15" t="n">
-        <v>359</v>
+        <v>10</v>
       </c>
       <c r="R15" t="n">
-        <v>457</v>
+        <v>350</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1838,17 +1842,17 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1430027896</t>
+          <t>1226758676</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1430027896</t>
+          <t>https://m.place.naver.com/place/1226758676</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1860,29 +1864,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>보성내과의원</t>
+          <t>아미엘연합의원</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>boseonglove@naver.com</t>
+          <t>whitekmg1@naver.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>054-975-8280</t>
+          <t>054-475-7582</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>경상북도 칠곡군 왜관읍 중앙로 242</t>
+          <t>경상북도 구미시 옥계북로 40</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.amiel.co.kr/</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1892,12 +1896,12 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1908,7 +1912,7 @@
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1917,13 +1921,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>85</v>
+        <v>529</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="R16" t="n">
-        <v>85</v>
+        <v>540</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1932,17 +1936,17 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>13258851</t>
+          <t>20713357</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13258851</t>
+          <t>https://m.place.naver.com/place/20713357</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1954,20 +1958,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>오앤정연합의원</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
+          <t>영남한빛의원</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>gunwigun_official@naver.com</t>
+        </is>
+      </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>054-464-7575</t>
+          <t>054-383-8275</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>경상북도 구미시 인동36길 15 2층3층</t>
+          <t>대구광역시 군위군 군위읍 중앙길 72</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2007,13 +2015,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>336</v>
+        <v>165</v>
       </c>
       <c r="Q17" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>340</v>
+        <v>165</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2022,17 +2030,17 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1505760191</t>
+          <t>13256929</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1505760191</t>
+          <t>https://m.place.naver.com/place/13256929</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -2044,24 +2052,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>영남한빛의원</t>
+          <t>옥계내과의원</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>gunwigun_official@naver.com</t>
+          <t>czzzus@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>054-383-8275</t>
+          <t>054-473-8275</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>대구광역시 군위군 군위읍 중앙길 72</t>
+          <t>경상북도 구미시 옥계북로 36 옥계메디칼타워</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2101,13 +2109,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>165</v>
+        <v>146</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>165</v>
+        <v>147</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2116,17 +2124,17 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>13256929</t>
+          <t>13257337</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13256929</t>
+          <t>https://m.place.naver.com/place/13257337</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -2138,24 +2146,24 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>옥계내과의원</t>
+          <t>한사랑의원</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>czzzus@naver.com</t>
+          <t>hansarang365@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>054-473-8275</t>
+          <t>054-834-8275</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>경상북도 구미시 옥계북로 36 옥계메디칼타워</t>
+          <t>경상북도 의성군 금성면 탑리길 21-1 한사랑의원</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2195,13 +2203,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>145</v>
+        <v>190</v>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="R19" t="n">
-        <v>146</v>
+        <v>196</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2210,17 +2218,17 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>13257337</t>
+          <t>13258423</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13257337</t>
+          <t>https://m.place.naver.com/place/13258423</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -2314,7 +2322,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -2326,29 +2334,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>한사랑의원</t>
+          <t>서울아산속내과의원</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>hansarang365@naver.com</t>
+          <t>seoulasansok7582@naver.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>054-834-8275</t>
+          <t>054-476-7575</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>경상북도 의성군 금성면 탑리길 21-1 한사랑의원</t>
+          <t>경상북도 구미시 인동36길 6 2층 201호</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.seoulasansok.com</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2374,7 +2382,7 @@
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -2383,13 +2391,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>190</v>
+        <v>99</v>
       </c>
       <c r="Q21" t="n">
-        <v>6</v>
+        <v>365</v>
       </c>
       <c r="R21" t="n">
-        <v>196</v>
+        <v>464</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2398,17 +2406,17 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>13258423</t>
+          <t>1430027896</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13258423</t>
+          <t>https://m.place.naver.com/place/1430027896</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -2420,39 +2428,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>365늘속편한내과의원</t>
+          <t>보성내과의원</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>wgsok@naver.com</t>
+          <t>boseonglove@naver.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>054-974-7070</t>
+          <t>054-975-8280</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>경상북도 칠곡군 왜관읍 중앙로 232 3층</t>
+          <t>경상북도 칠곡군 왜관읍 중앙로 242</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>http://www.365neulsok.co.kr/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2477,13 +2485,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>338</v>
+        <v>85</v>
       </c>
       <c r="Q22" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>348</v>
+        <v>85</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2492,17 +2500,17 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1226758676</t>
+          <t>13258851</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1226758676</t>
+          <t>https://m.place.naver.com/place/13258851</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -2517,7 +2525,11 @@
           <t>다윈마취통증의학과</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>ej_yui@naver.com</t>
+        </is>
+      </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
@@ -2592,7 +2604,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -2682,7 +2694,7 @@
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -2694,25 +2706,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>왜관병원</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr"/>
+          <t>신령의원</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>meschool24@naver.com</t>
+        </is>
+      </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>054-971-1004</t>
+          <t>054-335-9155</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>경상북도 칠곡군 왜관읍 군청2길 10</t>
+          <t>경상북도 영천시 신녕면 장수로 1688-1</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>http://imhope.com/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2722,7 +2738,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2747,13 +2763,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>157</v>
+        <v>49</v>
       </c>
       <c r="Q25" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="R25" t="n">
-        <v>176</v>
+        <v>51</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2762,17 +2778,17 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>11663033</t>
+          <t>13256783</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/11663033</t>
+          <t>https://m.place.naver.com/place/13256783</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -2784,29 +2800,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>석연합의원</t>
+          <t>삼성연합의원</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>seokunion@naver.com</t>
+          <t>lukeuc@naver.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>054-607-8275</t>
+          <t>054-971-7599</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>경상북도 구미시 수출대로31길 66</t>
+          <t>경상북도 칠곡군 왜관읍 중앙로 245-3</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>http://blog.naver.com/seokunion</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2816,12 +2832,12 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2841,13 +2857,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>159</v>
+        <v>117</v>
       </c>
       <c r="Q26" t="n">
-        <v>53</v>
+        <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>212</v>
+        <v>118</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2856,17 +2872,17 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>19866905</t>
+          <t>13258777</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/19866905</t>
+          <t>https://m.place.naver.com/place/13258777</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -2878,29 +2894,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>신령의원</t>
+          <t>왜관병원</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>yeongcheonsi@naver.com</t>
+          <t>the1eye_center@naver.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>054-335-9155</t>
+          <t>054-971-1004</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>경상북도 영천시 신녕면 장수로 1688-1</t>
+          <t>경상북도 칠곡군 왜관읍 군청2길 10</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://imhope.com/</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2910,7 +2926,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2935,13 +2951,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>49</v>
+        <v>157</v>
       </c>
       <c r="Q27" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="R27" t="n">
-        <v>51</v>
+        <v>176</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2950,17 +2966,17 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>13256783</t>
+          <t>11663033</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13256783</t>
+          <t>https://m.place.naver.com/place/11663033</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -2972,24 +2988,24 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>삼성연합의원</t>
+          <t>현대연합의원</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>lukeuc@naver.com</t>
+          <t>hd7629100@naver.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>054-971-7599</t>
+          <t>054-336-2277</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>경상북도 칠곡군 왜관읍 중앙로 245-3</t>
+          <t>경상북도 영천시 신녕면 장수로 1673</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3029,13 +3045,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>117</v>
+        <v>70</v>
       </c>
       <c r="Q28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R28" t="n">
-        <v>118</v>
+        <v>72</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3044,51 +3060,51 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>13258777</t>
+          <t>13256788</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13258777</t>
+          <t>https://m.place.naver.com/place/13256788</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>비뇨의학과</t>
+          <t>병원,의원</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>리세비뇨기과의원</t>
+          <t>석연합의원</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>binterest@naver.com</t>
+          <t>seokunion@naver.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>054-476-7585</t>
+          <t>054-607-8275</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>경상북도 구미시 옥계북로 36 옥계메디칼타워 3층</t>
+          <t>경상북도 구미시 수출대로31길 66</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://blog.naver.com/seokunion</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3098,12 +3114,12 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -3123,13 +3139,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>319</v>
+        <v>158</v>
       </c>
       <c r="Q29" t="n">
-        <v>2</v>
+        <v>54</v>
       </c>
       <c r="R29" t="n">
-        <v>321</v>
+        <v>212</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3138,17 +3154,17 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>13541236</t>
+          <t>19866905</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13541236</t>
+          <t>https://m.place.naver.com/place/19866905</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -3160,29 +3176,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>서비뇨기과의원</t>
+          <t>탑 비뇨기과의원</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>reflex8@naver.com</t>
+          <t>top-uro@naver.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>054-472-9996</t>
+          <t>054-473-4567</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>경상북도 구미시 인동중앙로 42</t>
+          <t>경상북도 구미시 인동가산로 35 2층 탑비뇨기과의원</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>http://cafe.naver.com/seouro</t>
+          <t>http://gumitop.co.kr</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3192,12 +3208,12 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -3217,13 +3233,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>310</v>
+        <v>241</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R30" t="n">
-        <v>310</v>
+        <v>248</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3232,17 +3248,17 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>13257328</t>
+          <t>34346774</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13257328</t>
+          <t>https://m.place.naver.com/place/34346774</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -3254,25 +3270,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>탑 비뇨기과의원</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr"/>
+          <t>리세비뇨기과의원</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>binterest@naver.com</t>
+        </is>
+      </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>054-473-4567</t>
+          <t>054-476-7585</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>경상북도 구미시 인동가산로 35 2층 탑비뇨기과의원</t>
+          <t>경상북도 구미시 옥계북로 36 옥계메디칼타워 3층</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>http://gumitop.co.kr</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3307,13 +3327,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>241</v>
+        <v>319</v>
       </c>
       <c r="Q31" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="R31" t="n">
-        <v>248</v>
+        <v>321</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3322,17 +3342,17 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>34346774</t>
+          <t>13541236</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/34346774</t>
+          <t>https://m.place.naver.com/place/13541236</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -3344,34 +3364,30 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>미라클의원</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>uready21@naver.com</t>
-        </is>
-      </c>
+          <t>서비뇨기과의원</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0507-1432-5995</t>
+          <t>054-472-9996</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>경상북도 구미시 인동가산로 11</t>
+          <t>경상북도 구미시 인동중앙로 42</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>http://www.miracleuro.com/</t>
+          <t>http://cafe.naver.com/seouro</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -3381,7 +3397,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3401,13 +3417,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>112</v>
+        <v>310</v>
       </c>
       <c r="Q32" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>115</v>
+        <v>310</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3416,60 +3432,56 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>12772679</t>
+          <t>13257328</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/12772679</t>
+          <t>https://m.place.naver.com/place/13257328</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>산부인과</t>
+          <t>비뇨의학과</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>삼성퀸스여성의원</t>
+          <t>미라클의원</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>tmddusrla31@naver.com</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>admin@squeens.co.kr</t>
-        </is>
-      </c>
+          <t>n-healingchoi@naver.com</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0507-1355-7078</t>
+          <t>0507-1432-5995</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>경상북도 칠곡군 왜관읍 중앙로 232 7층</t>
+          <t>경상북도 구미시 인동가산로 11</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>http://squeens.co.kr</t>
+          <t>http://www.miracleuro.com/</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -3479,7 +3491,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3499,13 +3511,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>53</v>
+        <v>112</v>
       </c>
       <c r="Q33" t="n">
-        <v>83</v>
+        <v>3</v>
       </c>
       <c r="R33" t="n">
-        <v>136</v>
+        <v>115</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3514,17 +3526,17 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1681619241</t>
+          <t>12772679</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1681619241</t>
+          <t>https://m.place.naver.com/place/12772679</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -3536,34 +3548,38 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>에바마레산부인과의원</t>
+          <t>삼성퀸스여성의원</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>nn0062@naver.com</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
+          <t>mung223@naver.com</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>admin@squeens.co.kr</t>
+        </is>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>054-475-4500</t>
+          <t>0507-1355-7078</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>경상북도 구미시 이계북로 141</t>
+          <t>경상북도 칠곡군 왜관읍 중앙로 232 7층</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>http://www.evamare.com/</t>
+          <t>http://squeens.co.kr</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -3573,7 +3589,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3593,13 +3609,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>976</v>
+        <v>53</v>
       </c>
       <c r="Q34" t="n">
-        <v>49</v>
+        <v>87</v>
       </c>
       <c r="R34" t="n">
-        <v>1025</v>
+        <v>140</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3608,17 +3624,17 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>11639285</t>
+          <t>1681619241</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/11639285</t>
+          <t>https://m.place.naver.com/place/1681619241</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -3630,29 +3646,29 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>아리아 여성의원</t>
+          <t>에바마레산부인과의원</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>cepc2000@naver.com</t>
+          <t>nn0062@naver.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0507-1313-0338</t>
+          <t>054-475-4500</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>경상북도 구미시 산동읍 신당1로2길 7 6층</t>
+          <t>경상북도 구미시 이계북로 141</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/cepc2000</t>
+          <t>http://www.evamare.com/</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3667,7 +3683,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -3687,13 +3703,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>82</v>
+        <v>976</v>
       </c>
       <c r="Q35" t="n">
-        <v>748</v>
+        <v>49</v>
       </c>
       <c r="R35" t="n">
-        <v>830</v>
+        <v>1025</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3702,51 +3718,51 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>2079097826</t>
+          <t>11639285</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2079097826</t>
+          <t>https://m.place.naver.com/place/11639285</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>소아청소년과</t>
+          <t>산부인과</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>에바마레소아청소년과의원</t>
+          <t>아리아 여성의원</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>sonvely93@naver.com</t>
+          <t>cepc2000@naver.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>054-476-2540</t>
+          <t>0507-1313-0338</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>경상북도 구미시 이계북로 141</t>
+          <t>경상북도 구미시 산동읍 신당1로2길 7 6층</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/cepc2000</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3756,12 +3772,12 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3781,13 +3797,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>129</v>
+        <v>99</v>
       </c>
       <c r="Q36" t="n">
-        <v>22</v>
+        <v>606</v>
       </c>
       <c r="R36" t="n">
-        <v>151</v>
+        <v>705</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3796,17 +3812,17 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>36772586</t>
+          <t>2079097826</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36772586</t>
+          <t>https://m.place.naver.com/place/2079097826</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -3875,13 +3891,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="Q37" t="n">
         <v>2</v>
       </c>
       <c r="R37" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3900,7 +3916,7 @@
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -3912,29 +3928,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>봄연합소아청소년과의원</t>
+          <t>아이큰소아청소년과의원</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>mygoodandjoy@naver.com</t>
+          <t>ikeun0808@naver.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0507-1418-9502</t>
+          <t>054-476-0808</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>경상북도 구미시 산호대로31길 15 메디파크 4층</t>
+          <t>경상북도 구미시 산동읍 신당1로3길 19 2층</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/ikeun0808</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3944,12 +3960,12 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3965,17 +3981,17 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1125</v>
+        <v>187</v>
       </c>
       <c r="Q38" t="n">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="R38" t="n">
-        <v>1149</v>
+        <v>232</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -3984,17 +4000,17 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>19810114</t>
+          <t>1461221122</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/19810114</t>
+          <t>https://m.place.naver.com/place/1461221122</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -4006,29 +4022,25 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>아이큰소아청소년과의원</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>ikeun0808@naver.com</t>
-        </is>
-      </c>
+          <t>에바마레소아청소년과의원</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>054-476-0808</t>
+          <t>054-476-2540</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>경상북도 구미시 산동읍 신당1로3길 19 2층</t>
+          <t>경상북도 구미시 이계북로 141</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ikeun0808</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4038,12 +4050,12 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -4059,17 +4071,17 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P39" t="n">
-        <v>187</v>
+        <v>129</v>
       </c>
       <c r="Q39" t="n">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="R39" t="n">
-        <v>230</v>
+        <v>151</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4078,51 +4090,51 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>1461221122</t>
+          <t>36772586</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1461221122</t>
+          <t>https://m.place.naver.com/place/36772586</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>신경과</t>
+          <t>소아청소년과</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>명연합신경과의원</t>
+          <t>봄연합소아청소년과의원</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>nrdoc@naver.com</t>
+          <t>mygoodandjoy@naver.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>054-458-7722</t>
+          <t>0507-1418-9502</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>경상북도 구미시 인동중앙로 39 2층</t>
+          <t>경상북도 구미시 산호대로31길 15 메디파크 4층</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>http://www.mneuro.co.kr/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4132,12 +4144,12 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -4157,13 +4169,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>76</v>
+        <v>1125</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="R40" t="n">
-        <v>76</v>
+        <v>1149</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4172,51 +4184,51 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>36449199</t>
+          <t>19810114</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36449199</t>
+          <t>https://m.place.naver.com/place/19810114</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>외과</t>
+          <t>신경과</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>장천외과의원</t>
+          <t>명연합신경과의원</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ayeonmaen87@naver.com</t>
+          <t>nrdoc@naver.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>054-473-7800</t>
+          <t>054-458-7722</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>경상북도 구미시 장천면 강동로 207-5</t>
+          <t>경상북도 구미시 인동중앙로 39 2층</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.mneuro.co.kr/</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4226,12 +4238,12 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -4251,13 +4263,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4266,17 +4278,17 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>11639156</t>
+          <t>36449199</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/11639156</t>
+          <t>https://m.place.naver.com/place/36449199</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -4291,11 +4303,7 @@
           <t>삼성연합의원</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>lukeuc@naver.com</t>
-        </is>
-      </c>
+      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
@@ -4345,13 +4353,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1676</v>
+        <v>1677</v>
       </c>
       <c r="Q42" t="n">
-        <v>582</v>
+        <v>592</v>
       </c>
       <c r="R42" t="n">
-        <v>2258</v>
+        <v>2269</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4370,7 +4378,7 @@
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -4442,10 +4450,10 @@
         <v>31</v>
       </c>
       <c r="Q43" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R43" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4464,7 +4472,7 @@
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -4536,10 +4544,10 @@
         <v>903</v>
       </c>
       <c r="Q44" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="R44" t="n">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4558,7 +4566,7 @@
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -4627,13 +4635,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="Q45" t="n">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="R45" t="n">
-        <v>1286</v>
+        <v>1289</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4652,7 +4660,7 @@
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -4664,24 +4672,20 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>석적영남정형외과의원</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>skjk-4084@naver.com</t>
-        </is>
-      </c>
+          <t>탑정형외과연합의원</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>054-976-8275</t>
+          <t>054-475-5119</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>경상북도 칠곡군 석적읍 북중리3길 33</t>
+          <t>경상북도 구미시 산호대로25길 4-4</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -4721,13 +4725,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>405</v>
+        <v>215</v>
       </c>
       <c r="Q46" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R46" t="n">
-        <v>410</v>
+        <v>219</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4736,17 +4740,17 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>12777213</t>
+          <t>21661063</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/12777213</t>
+          <t>https://m.place.naver.com/place/21661063</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -4761,7 +4765,11 @@
           <t>산동튼튼정형외과의원</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr"/>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>topten0012@naver.com</t>
+        </is>
+      </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
@@ -4836,7 +4844,7 @@
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -4848,44 +4856,44 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>탑정형외과연합의원</t>
+          <t>기찬마취통증의학과의원 구미</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>chyu00@naver.com</t>
+          <t>gicha001@naver.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>054-475-5119</t>
+          <t>0507-1425-9775</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>경상북도 구미시 산호대로25길 4-4</t>
+          <t>경상북도 구미시 인동중앙로 15 이트리뷴타워 3층</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.gichanpain.co.kr</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -4901,17 +4909,17 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P48" t="n">
-        <v>215</v>
+        <v>950</v>
       </c>
       <c r="Q48" t="n">
-        <v>4</v>
+        <v>1954</v>
       </c>
       <c r="R48" t="n">
-        <v>219</v>
+        <v>2904</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4920,17 +4928,17 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>21661063</t>
+          <t>35608810</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/21661063</t>
+          <t>https://m.place.naver.com/place/35608810</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -4942,44 +4950,44 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>기찬마취통증의학과의원 구미</t>
+          <t>석적영남정형외과의원</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>gicha001@naver.com</t>
+          <t>chilgok6043@naver.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0507-1425-9775</t>
+          <t>054-976-8275</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>경상북도 구미시 인동중앙로 15 이트리뷴타워 3층</t>
+          <t>경상북도 칠곡군 석적읍 북중리3길 33</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>http://www.gichanpain.co.kr</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -4995,17 +5003,17 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P49" t="n">
-        <v>950</v>
+        <v>406</v>
       </c>
       <c r="Q49" t="n">
-        <v>1949</v>
+        <v>5</v>
       </c>
       <c r="R49" t="n">
-        <v>2899</v>
+        <v>411</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -5014,17 +5022,17 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>35608810</t>
+          <t>12777213</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35608810</t>
+          <t>https://m.place.naver.com/place/12777213</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -5093,13 +5101,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>308</v>
+        <v>351</v>
       </c>
       <c r="Q50" t="n">
-        <v>121</v>
+        <v>145</v>
       </c>
       <c r="R50" t="n">
-        <v>429</v>
+        <v>496</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5118,7 +5126,7 @@
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -5130,29 +5138,25 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>더찾는한의원</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>morecomehani@naver.com</t>
-        </is>
-      </c>
+          <t>신세계한의원</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0507-1318-8908</t>
+          <t>054-471-4477</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>경상북도 구미시 인동36길 6 성원빌딩 2층 202호</t>
+          <t>경상북도 구미시 인동북길 83 동산빌딩 2층</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/morecomehani</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5162,12 +5166,12 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -5183,17 +5187,17 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P51" t="n">
-        <v>791</v>
+        <v>170</v>
       </c>
       <c r="Q51" t="n">
-        <v>3945</v>
+        <v>3</v>
       </c>
       <c r="R51" t="n">
-        <v>4736</v>
+        <v>173</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5202,17 +5206,17 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>2049265297</t>
+          <t>13257303</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2049265297</t>
+          <t>https://m.place.naver.com/place/13257303</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -5224,24 +5228,20 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>천수한의원</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>ssgyjb@naver.com</t>
-        </is>
-      </c>
+          <t>왜관한의원</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>054-977-1230</t>
+          <t>054-975-8875</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>경상북도 칠곡군 석적읍 북중리3길 67 천수한의원</t>
+          <t>경상북도 칠곡군 왜관읍 중앙로 237</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -5281,13 +5281,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>166</v>
+        <v>70</v>
       </c>
       <c r="Q52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R52" t="n">
-        <v>168</v>
+        <v>71</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5296,17 +5296,17 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>13258870</t>
+          <t>35408952</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13258870</t>
+          <t>https://m.place.naver.com/place/35408952</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -5318,29 +5318,29 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>맑은숲한의원 구미</t>
+          <t>소망한의원</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ddalgi3807@naver.com</t>
+          <t>chltnr2212@naver.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0507-1411-1076</t>
+          <t>054-473-1461</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>경상북도 구미시 인동가산로 17 태송빌딩 4층</t>
+          <t>경상북도 구미시 검성로 48 1층</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>http://www.o2clinic.co.kr/index_intro.php?page=html&amp;br_cd=56&amp;mc=020101</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5350,7 +5350,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -5375,13 +5375,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1050</v>
+        <v>2</v>
       </c>
       <c r="Q53" t="n">
-        <v>1358</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>2408</v>
+        <v>2</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5390,17 +5390,17 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>11381684</t>
+          <t>2097432700</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/11381684</t>
+          <t>https://m.place.naver.com/place/2097432700</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -5412,29 +5412,29 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>미담한의원 구미</t>
+          <t>보생한의원</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>midamgm@naver.com</t>
+          <t>kmd_cho@naver.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>054-471-1075</t>
+          <t>054-476-7676</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>경상북도 구미시 옥계북로 26 2층</t>
+          <t>경상북도 구미시 옥계북로 36 메디칼타워</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/midamgm</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5444,12 +5444,12 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -5469,13 +5469,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>140</v>
+        <v>96</v>
       </c>
       <c r="Q54" t="n">
-        <v>720</v>
+        <v>1</v>
       </c>
       <c r="R54" t="n">
-        <v>860</v>
+        <v>97</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5484,17 +5484,17 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>30836395</t>
+          <t>20337090</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/30836395</t>
+          <t>https://m.place.naver.com/place/20337090</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -5506,20 +5506,24 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>군위한의원</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr"/>
+          <t>해산한의원</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>pjskwj@naver.com</t>
+        </is>
+      </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>054-382-0177</t>
+          <t>054-471-0051</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>대구광역시 군위군 군위읍 중앙길 116</t>
+          <t>경상북도 구미시 인동가산로 31 쌍둥이빌딩 3층</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -5559,13 +5563,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>48</v>
+        <v>219</v>
       </c>
       <c r="Q55" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R55" t="n">
-        <v>49</v>
+        <v>223</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5574,17 +5578,17 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>1120556317</t>
+          <t>12034751</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1120556317</t>
+          <t>https://m.place.naver.com/place/12034751</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -5596,25 +5600,29 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>신세계한의원</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr"/>
+          <t>미담한의원 구미</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>midamgm@naver.com</t>
+        </is>
+      </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>054-471-4477</t>
+          <t>054-471-1075</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>경상북도 구미시 인동북길 83 동산빌딩 2층</t>
+          <t>경상북도 구미시 옥계북로 26 2층</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/midamgm</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5624,12 +5632,12 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -5649,13 +5657,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>170</v>
+        <v>141</v>
       </c>
       <c r="Q56" t="n">
-        <v>3</v>
+        <v>719</v>
       </c>
       <c r="R56" t="n">
-        <v>173</v>
+        <v>860</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5664,17 +5672,17 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>13257303</t>
+          <t>30836395</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13257303</t>
+          <t>https://m.place.naver.com/place/30836395</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -5686,24 +5694,24 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>대원한의원</t>
+          <t>석산한의원</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>daiwonhani@naver.com</t>
+          <t>missskj7539@naver.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>054-382-7582</t>
+          <t>054-383-1694</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>대구광역시 군위군 군위읍 중앙길 91</t>
+          <t>대구광역시 군위군 삼국유사면 석산길 233</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -5743,13 +5751,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>36</v>
+        <v>110</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="R57" t="n">
-        <v>36</v>
+        <v>125</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5758,17 +5766,17 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>31961391</t>
+          <t>37350475</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31961391</t>
+          <t>https://m.place.naver.com/place/37350475</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -5780,29 +5788,29 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>열린한의원 구미</t>
+          <t>천수한의원</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>openhani5999@naver.com</t>
+          <t>ssgyjb@naver.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0507-1327-5999</t>
+          <t>054-977-1230</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>경상북도 구미시 산동읍 신당1로3길 19 1동 201, 202호</t>
+          <t>경상북도 칠곡군 석적읍 북중리3길 67 천수한의원</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>http://openhani.co.kr</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5812,7 +5820,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -5833,17 +5841,17 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P58" t="n">
-        <v>353</v>
+        <v>166</v>
       </c>
       <c r="Q58" t="n">
-        <v>848</v>
+        <v>2</v>
       </c>
       <c r="R58" t="n">
-        <v>1201</v>
+        <v>168</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5852,17 +5860,17 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>1598704779</t>
+          <t>13258870</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1598704779</t>
+          <t>https://m.place.naver.com/place/13258870</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -5874,30 +5882,34 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>석산한의원</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr"/>
+          <t>후한의원 구미점</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>hoban2011902@naver.com</t>
+        </is>
+      </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>054-383-1694</t>
+          <t>054-474-1075</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>대구광역시 군위군 삼국유사면 석산길 233</t>
+          <t>경상북도 구미시 인동가산로 9-3 노블레스타워 4층</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://m.site.naver.com/26l7M</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -5907,7 +5919,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -5918,22 +5930,22 @@
       <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P59" t="n">
-        <v>110</v>
+        <v>170</v>
       </c>
       <c r="Q59" t="n">
-        <v>15</v>
+        <v>1046</v>
       </c>
       <c r="R59" t="n">
-        <v>125</v>
+        <v>1216</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -5942,17 +5954,17 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>37350475</t>
+          <t>21602725</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37350475</t>
+          <t>https://m.place.naver.com/place/21602725</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -5964,34 +5976,34 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>후한의원 구미점</t>
+          <t>군위한의원</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>hoban2011902@naver.com</t>
+          <t>jundragon94@naver.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>054-474-1075</t>
+          <t>054-382-0177</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>경상북도 구미시 인동가산로 9-3 노블레스타워 4층</t>
+          <t>대구광역시 군위군 군위읍 중앙길 116</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://hoogumi.imweb.me</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -6001,7 +6013,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -6012,22 +6024,22 @@
       <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P60" t="n">
-        <v>168</v>
+        <v>48</v>
       </c>
       <c r="Q60" t="n">
-        <v>1035</v>
+        <v>1</v>
       </c>
       <c r="R60" t="n">
-        <v>1203</v>
+        <v>49</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6036,17 +6048,17 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>21602725</t>
+          <t>1120556317</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/21602725</t>
+          <t>https://m.place.naver.com/place/1120556317</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -6118,10 +6130,10 @@
         <v>156</v>
       </c>
       <c r="Q61" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="R61" t="n">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6140,7 +6152,7 @@
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -6152,29 +6164,29 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>광동한의원</t>
+          <t>마추펴추한의원</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>kd107501@naver.com</t>
+          <t>mcpc_clinic@naver.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>054-472-1275</t>
+          <t>054-474-7555</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>경상북도 구미시 인동36길 9 금강빌딩</t>
+          <t>경상북도 구미시 산동읍 신당1로3길 3 3층 301호</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/mcpc_clinic</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -6184,12 +6196,12 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -6205,17 +6217,17 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P62" t="n">
-        <v>21</v>
+        <v>171</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="R62" t="n">
-        <v>21</v>
+        <v>210</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6224,17 +6236,17 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>13257315</t>
+          <t>1448795064</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13257315</t>
+          <t>https://m.place.naver.com/place/1448795064</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -6246,24 +6258,24 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>평강한의원</t>
+          <t>김영남한의원</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>jsg0326@naver.com</t>
+          <t>yasiya21@naver.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>054-471-2302</t>
+          <t>054-977-9090</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>경상북도 구미시 인동중앙로 50 금오상가 2층 201호</t>
+          <t>경상북도 칠곡군 왜관읍 시장1길 6 2층</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -6303,13 +6315,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>254</v>
+        <v>76</v>
       </c>
       <c r="Q63" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R63" t="n">
-        <v>258</v>
+        <v>77</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6318,17 +6330,17 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>32848252</t>
+          <t>815134315</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32848252</t>
+          <t>https://m.place.naver.com/place/815134315</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -6340,34 +6352,34 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>왜관한의원</t>
+          <t>함소아한의원 구미</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>yasiya21@naver.com</t>
+          <t>gumihamsoa2@naver.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>054-975-8875</t>
+          <t>054-457-1075</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>경상북도 칠곡군 왜관읍 중앙로 237</t>
+          <t>경상북도 구미시 산동읍 신당1로3길 19 골드타워 3층 303호</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.hamsoa.com/reservation/01_v/60/</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -6377,7 +6389,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -6388,22 +6400,22 @@
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P64" t="n">
-        <v>70</v>
+        <v>186</v>
       </c>
       <c r="Q64" t="n">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="R64" t="n">
-        <v>71</v>
+        <v>223</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6412,17 +6424,17 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>35408952</t>
+          <t>11885509</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35408952</t>
+          <t>https://m.place.naver.com/place/11885509</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -6434,25 +6446,29 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>김영남한의원</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr"/>
+          <t>맑은숲한의원 구미</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>ddalgi3807@naver.com</t>
+        </is>
+      </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>054-977-9090</t>
+          <t>0507-1411-1076</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>경상북도 칠곡군 왜관읍 시장1길 6 2층</t>
+          <t>경상북도 구미시 인동가산로 17 태송빌딩 4층</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.o2clinic.co.kr/index_intro.php?page=html&amp;br_cd=56&amp;mc=020101</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -6462,7 +6478,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -6487,13 +6503,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>76</v>
+        <v>1052</v>
       </c>
       <c r="Q65" t="n">
-        <v>1</v>
+        <v>1352</v>
       </c>
       <c r="R65" t="n">
-        <v>77</v>
+        <v>2404</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6502,17 +6518,17 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>815134315</t>
+          <t>11381684</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/815134315</t>
+          <t>https://m.place.naver.com/place/11381684</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -6524,20 +6540,20 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>안성한의원</t>
+          <t>명성한의원</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>054-977-7582</t>
+          <t>054-974-1540</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>경상북도 칠곡군 석적읍 북중리3길 48</t>
+          <t>경상북도 칠곡군 왜관읍 중앙로 247-1</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -6577,13 +6593,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="R66" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6592,17 +6608,17 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>13258874</t>
+          <t>19522896</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13258874</t>
+          <t>https://m.place.naver.com/place/19522896</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -6614,34 +6630,34 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>함소아한의원 구미</t>
+          <t>안성한의원</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>gumihamsoa2@naver.com</t>
+          <t>anseongnature34@naver.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>054-457-1075</t>
+          <t>054-977-7582</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>경상북도 구미시 산동읍 신당1로3길 19 골드타워 3층 303호</t>
+          <t>경상북도 칠곡군 석적읍 북중리3길 48</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://www.hamsoa.com/reservation/01_v/60/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -6651,7 +6667,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -6662,22 +6678,22 @@
       <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P67" t="n">
-        <v>181</v>
+        <v>81</v>
       </c>
       <c r="Q67" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>218</v>
+        <v>81</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6686,17 +6702,17 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>11885509</t>
+          <t>13258874</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/11885509</t>
+          <t>https://m.place.naver.com/place/13258874</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -6708,29 +6724,29 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>산동경희한의원</t>
+          <t>홍제한의원</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>sandongkh@naver.com</t>
+          <t>hongjehan@naver.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>054-471-3377</t>
+          <t>054-973-8946</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>경상북도 구미시 산동읍 신당2로 29 대호프라자 3층 303호</t>
+          <t>경상북도 칠곡군 왜관읍 중앙로 252</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sandongkh</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6740,12 +6756,12 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -6761,17 +6777,17 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P68" t="n">
-        <v>276</v>
+        <v>22</v>
       </c>
       <c r="Q68" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>285</v>
+        <v>22</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6780,17 +6796,17 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>1082453617</t>
+          <t>13258815</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1082453617</t>
+          <t>https://m.place.naver.com/place/13258815</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -6802,25 +6818,29 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>해산한의원</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr"/>
+          <t>마음과마음한의원</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>realkiva@naver.com</t>
+        </is>
+      </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>054-471-0051</t>
+          <t>054-476-2097</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>경상북도 구미시 인동가산로 31 쌍둥이빌딩 3층</t>
+          <t>경상북도 구미시 옥계북로 94 제일빌딩 2층</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/realkiva</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6830,12 +6850,12 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -6855,13 +6875,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>219</v>
+        <v>102</v>
       </c>
       <c r="Q69" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R69" t="n">
-        <v>223</v>
+        <v>103</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6870,17 +6890,17 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>12034751</t>
+          <t>32803500</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/12034751</t>
+          <t>https://m.place.naver.com/place/32803500</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -6892,20 +6912,24 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>홍제한의원</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr"/>
+          <t>대흥한의원</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>kindari@naver.com</t>
+        </is>
+      </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>054-973-8946</t>
+          <t>054-382-7056</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>경상북도 칠곡군 왜관읍 중앙로 252</t>
+          <t>대구광역시 군위군 의흥면 읍내길 32-6</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -6945,13 +6969,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="Q70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R70" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -6960,17 +6984,17 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>13258815</t>
+          <t>462523159</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13258815</t>
+          <t>https://m.place.naver.com/place/462523159</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -6982,29 +7006,29 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>소나무한의원</t>
+          <t>산동경희한의원</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>hori73@naver.com</t>
+          <t>sandongkh@naver.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>054-472-8325</t>
+          <t>054-471-3377</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>경상북도 구미시 인동중앙로10길 5</t>
+          <t>경상북도 구미시 산동읍 신당2로 29 대호프라자 3층 303호</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/sandongkh</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -7014,12 +7038,12 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -7035,17 +7059,17 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P71" t="n">
-        <v>16</v>
+        <v>277</v>
       </c>
       <c r="Q71" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="R71" t="n">
-        <v>17</v>
+        <v>286</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7054,17 +7078,17 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>13257327</t>
+          <t>1082453617</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13257327</t>
+          <t>https://m.place.naver.com/place/1082453617</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -7076,29 +7100,29 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>마음과마음한의원</t>
+          <t>열린한의원 구미</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>realkiva@naver.com</t>
+          <t>openhani5999@naver.com</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>054-476-2097</t>
+          <t>0507-1327-5999</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>경상북도 구미시 옥계북로 94 제일빌딩 2층</t>
+          <t>경상북도 구미시 산동읍 신당1로3길 19 1동 201, 202호</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/realkiva</t>
+          <t>http://openhani.co.kr</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -7113,7 +7137,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -7129,17 +7153,17 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P72" t="n">
-        <v>102</v>
+        <v>356</v>
       </c>
       <c r="Q72" t="n">
-        <v>1</v>
+        <v>856</v>
       </c>
       <c r="R72" t="n">
-        <v>103</v>
+        <v>1212</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7148,17 +7172,17 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>32803500</t>
+          <t>1598704779</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32803500</t>
+          <t>https://m.place.naver.com/place/1598704779</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -7170,20 +7194,20 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>대흥한의원</t>
+          <t>평강한의원</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>054-382-7056</t>
+          <t>054-471-2302</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>대구광역시 군위군 의흥면 읍내길 32-6</t>
+          <t>경상북도 구미시 인동중앙로 50 금오상가 2층 201호</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -7223,13 +7247,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>35</v>
+        <v>254</v>
       </c>
       <c r="Q73" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R73" t="n">
-        <v>36</v>
+        <v>258</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7238,17 +7262,17 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>462523159</t>
+          <t>32848252</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/462523159</t>
+          <t>https://m.place.naver.com/place/32848252</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -7260,20 +7284,24 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>보생한의원</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr"/>
+          <t>대원한의원</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>daiwonhani@naver.com</t>
+        </is>
+      </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>054-476-7676</t>
+          <t>054-382-7582</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>경상북도 구미시 옥계북로 36 메디칼타워</t>
+          <t>대구광역시 군위군 군위읍 중앙길 91</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -7313,13 +7341,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>96</v>
+        <v>36</v>
       </c>
       <c r="Q74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>97</v>
+        <v>36</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7328,17 +7356,17 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>20337090</t>
+          <t>31961391</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20337090</t>
+          <t>https://m.place.naver.com/place/31961391</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -7350,24 +7378,24 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>명성한의원</t>
+          <t>소나무한의원</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>kofam311@naver.com</t>
+          <t>sikim6478@naver.com</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>054-974-1540</t>
+          <t>054-472-8325</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>경상북도 칠곡군 왜관읍 중앙로 247-1</t>
+          <t>경상북도 구미시 인동중앙로10길 5</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -7407,13 +7435,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="Q75" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="R75" t="n">
-        <v>79</v>
+        <v>17</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7422,17 +7450,17 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>19522896</t>
+          <t>13257327</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/19522896</t>
+          <t>https://m.place.naver.com/place/13257327</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -7444,29 +7472,29 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>마추펴추한의원</t>
+          <t>더찾는한의원</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>mcpc_clinic@naver.com</t>
+          <t>morecomehani@naver.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>054-474-7555</t>
+          <t>0507-1318-8908</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>경상북도 구미시 산동읍 신당1로3길 3 3층 301호</t>
+          <t>경상북도 구미시 인동36길 6 성원빌딩 2층 202호</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mcpc_clinic</t>
+          <t>https://blog.naver.com/morecomehani</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -7501,13 +7529,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>171</v>
+        <v>831</v>
       </c>
       <c r="Q76" t="n">
-        <v>39</v>
+        <v>4045</v>
       </c>
       <c r="R76" t="n">
-        <v>210</v>
+        <v>4876</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7516,17 +7544,17 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>1448795064</t>
+          <t>2049265297</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1448795064</t>
+          <t>https://m.place.naver.com/place/2049265297</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
